--- a/Team-Data/2020-21/1-19-2020-21.xlsx
+++ b/Team-Data/2020-21/1-19-2020-21.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         <v>5.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z4" t="n">
         <v>18.5</v>
@@ -1200,7 +1200,7 @@
         <v>13</v>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
         <v>6</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
         <v>19</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
         <v>21</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ8" t="n">
         <v>21</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -2229,16 +2229,16 @@
         <v>11.1</v>
       </c>
       <c r="S10" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T10" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U10" t="n">
         <v>24.5</v>
       </c>
       <c r="V10" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
@@ -2316,7 +2316,7 @@
         <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
         <v>9</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>41.6</v>
       </c>
       <c r="J16" t="n">
-        <v>92.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="K16" t="n">
         <v>0.452</v>
@@ -3318,13 +3318,13 @@
         <v>0.765</v>
       </c>
       <c r="R16" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S16" t="n">
         <v>34.8</v>
       </c>
       <c r="T16" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U16" t="n">
         <v>27.2</v>
@@ -3396,7 +3396,7 @@
         <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
         <v>16</v>
@@ -3414,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
         <v>29</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         <v>15.9</v>
       </c>
       <c r="M18" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="N18" t="n">
         <v>0.403</v>
@@ -3700,7 +3700,7 @@
         <v>9.1</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y18" t="n">
         <v>5.1</v>
@@ -3748,7 +3748,7 @@
         <v>4</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
@@ -3778,7 +3778,7 @@
         <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY18" t="n">
         <v>13</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
         <v>18</v>
       </c>
       <c r="AR21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
         <v>11</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
         <v>16</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW27" t="n">
         <v>28</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-19-2020-21</t>
+          <t>2021-01-19</t>
         </is>
       </c>
     </row>
